--- a/Albums List.xlsx
+++ b/Albums List.xlsx
@@ -2125,7 +2125,7 @@
     <t>Miracle Musical</t>
   </si>
   <si>
-    <t>Pop, Rap, Balad</t>
+    <t>Pop, Rap, Ballad</t>
   </si>
   <si>
     <t>When We Were Friends</t>
@@ -3556,7 +3556,7 @@
     <t>Laufey</t>
   </si>
   <si>
-    <t>Jazz Pop, Ballads, Modern Classical</t>
+    <t>Jazz Pop, Ballad, Modern Classical</t>
   </si>
   <si>
     <t>CASIOPEA</t>
@@ -17635,7 +17635,7 @@
       <c r="C307" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="D307" s="15" t="s">
+      <c r="D307" s="13" t="s">
         <v>696</v>
       </c>
       <c r="E307" s="15" t="s">

--- a/Albums List.xlsx
+++ b/Albums List.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3415" uniqueCount="1337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3421" uniqueCount="1341">
   <si>
     <t>RECORDS</t>
   </si>
@@ -44,7 +44,7 @@
     <t>Album</t>
   </si>
   <si>
-    <t>Alternative/Indie</t>
+    <t>Alternative, Indie</t>
   </si>
   <si>
     <t>English</t>
@@ -353,7 +353,7 @@
     <t>Everything Everything</t>
   </si>
   <si>
-    <t>Alternative/Indie, Art Rock, Indie Pop, Electronic</t>
+    <t>Alternative, Indie, Art Rock, Indie Pop, Electronic</t>
   </si>
   <si>
     <t>Raw Data Feel</t>
@@ -823,6 +823,9 @@
     <t>Crumb</t>
   </si>
   <si>
+    <t>Indie Rock, Pop Rock, Pop</t>
+  </si>
+  <si>
     <t>Aquemini</t>
   </si>
   <si>
@@ -907,7 +910,7 @@
     <t>The Clash</t>
   </si>
   <si>
-    <t>New Wave, Post-Punk</t>
+    <t>New Wave, Post Punk</t>
   </si>
   <si>
     <t>First Impression Of Earth</t>
@@ -958,7 +961,7 @@
     <t>Paul McCartney &amp; Various Artists</t>
   </si>
   <si>
-    <t>Alternative/Indie, Rock</t>
+    <t>Alternative, Indie, Rock</t>
   </si>
   <si>
     <t>This Is Happening</t>
@@ -1003,7 +1006,7 @@
     <t>Joaquin Sabina</t>
   </si>
   <si>
-    <t>Pop/Rock, Hard Rock</t>
+    <t>Pop Rock, Hard Rock</t>
   </si>
   <si>
     <t>Applefork</t>
@@ -1021,7 +1024,7 @@
     <t>The Age Of The Understatement</t>
   </si>
   <si>
-    <t>Indie Rock, Pop/Rock</t>
+    <t>Indie Rock, Pop Rock</t>
   </si>
   <si>
     <t>Colour Of The Trap</t>
@@ -1054,7 +1057,7 @@
     <t>Milmine</t>
   </si>
   <si>
-    <t>Alternative/Indie, Pop</t>
+    <t>Alternative, Indie, Pop</t>
   </si>
   <si>
     <t>Dudas Y Flores</t>
@@ -1090,7 +1093,7 @@
     <t>Los Años Mejores</t>
   </si>
   <si>
-    <t>Alternative/Indie Pop, Argentinian Rock</t>
+    <t>Alternative, Indie Pop, Argentinian Rock</t>
   </si>
   <si>
     <t>Rumours</t>
@@ -1129,7 +1132,7 @@
     <t>R.E.M</t>
   </si>
   <si>
-    <t>Alternative Rock, Pop/Rock</t>
+    <t>Alternative Rock, Pop Rock</t>
   </si>
   <si>
     <t>Lo mas lejos a tu lado</t>
@@ -1183,7 +1186,7 @@
     <t>El Niño De La Hipoteca</t>
   </si>
   <si>
-    <t xml:space="preserve">Pop/Rock </t>
+    <t xml:space="preserve">Pop Rock </t>
   </si>
   <si>
     <t>My Favourite Things</t>
@@ -1201,7 +1204,7 @@
     <t>Amaarae</t>
   </si>
   <si>
-    <t>Pop, Ryhtm&amp;Blues</t>
+    <t>Pop, R&amp;B</t>
   </si>
   <si>
     <t>EASY</t>
@@ -1261,7 +1264,7 @@
     <t>Monsieur Periné</t>
   </si>
   <si>
-    <t>Alternative/Indie, Tropipop, Spanish Rock</t>
+    <t>Alternative, Indie, Tropipop, Spanish Rock</t>
   </si>
   <si>
     <t>The Most Beautiful Moment in Life Pt.2</t>
@@ -1456,7 +1459,7 @@
     <t>Rex Orange County</t>
   </si>
   <si>
-    <t>Indie Hiphop, Indie Pop/Rock</t>
+    <t>Indie Hiphop, Indie Pop Rock</t>
   </si>
   <si>
     <t>Grace</t>
@@ -1546,7 +1549,7 @@
     <t>Panic! At The Disco</t>
   </si>
   <si>
-    <t>Pop, Pop/Rock</t>
+    <t>Pop, Pop Rock</t>
   </si>
   <si>
     <t>Antes de que cuente diez</t>
@@ -1609,13 +1612,13 @@
     <t>GLOOM DIVISION</t>
   </si>
   <si>
-    <t>Indie Pop, Post-Punk</t>
+    <t>Indie Pop, Post Punk</t>
   </si>
   <si>
     <t>Franz Ferdinand</t>
   </si>
   <si>
-    <t>Indie Rock, Post-Punk Revival, Dance Punk</t>
+    <t>Indie Rock, Post Punk Revival, Dance Punk</t>
   </si>
   <si>
     <t>9,25</t>
@@ -1681,7 +1684,7 @@
     <t>The Correspondents</t>
   </si>
   <si>
-    <t>Alternative/Indie, Electronic</t>
+    <t>Alternative, Indie, Electronic</t>
   </si>
   <si>
     <t>(What's The Story) Morning Glory?</t>
@@ -1741,7 +1744,7 @@
     <t>I Love You So F***ing Much</t>
   </si>
   <si>
-    <t>Alternative/Indie, Indie Rock</t>
+    <t>Alternative, Indie, Indie Rock</t>
   </si>
   <si>
     <t>zero_one</t>
@@ -1759,15 +1762,12 @@
     <t>Bruno Mars</t>
   </si>
   <si>
-    <t>Pop, Ryhtm&amp;Blues, Funk</t>
+    <t>Pop, R&amp;B, Funk</t>
   </si>
   <si>
     <t>Doo-Wops &amp; Hooligans</t>
   </si>
   <si>
-    <t>Pop, R&amp;B</t>
-  </si>
-  <si>
     <t>24K Magic</t>
   </si>
   <si>
@@ -1864,7 +1864,7 @@
     <t>Melatonin Dreams</t>
   </si>
   <si>
-    <t>Alternative/Indie, Folk</t>
+    <t>Alternative, Indie, Folk</t>
   </si>
   <si>
     <t>WHEN WE ALL FALL ASLEEP, WHERE DO WE GO?</t>
@@ -1936,13 +1936,13 @@
     <t>Why'd You Only Call Me When You're High?</t>
   </si>
   <si>
-    <t xml:space="preserve">Alternative/Indie Rock </t>
+    <t xml:space="preserve">Alternative, Indie Rock </t>
   </si>
   <si>
     <t>Do I Wanna Know</t>
   </si>
   <si>
-    <t>Alternative/Indie, Pop, Rock</t>
+    <t>Alternative, Indie, Pop, Rock</t>
   </si>
   <si>
     <t>One For The Road</t>
@@ -1954,7 +1954,7 @@
     <t>Art Rock, Psychedelic Pop</t>
   </si>
   <si>
-    <t>Alternative/Indie, Lounge, Jazz</t>
+    <t>Alternative, Indie, Lounge, Jazz</t>
   </si>
   <si>
     <t>Pony</t>
@@ -2002,7 +2002,7 @@
     <t>The Chaos Chapter: FIGHT OR ESCAPE</t>
   </si>
   <si>
-    <t>KPop, Pop/Rock</t>
+    <t>KPop, Pop Rock</t>
   </si>
   <si>
     <t>Not A Cover Band</t>
@@ -2098,7 +2098,7 @@
     <t>CA7RIEL &amp; Paco Amoroso</t>
   </si>
   <si>
-    <t>Alternative/Indie, Hiphop</t>
+    <t>Alternative, Indie, Hiphop</t>
   </si>
   <si>
     <t>Para Mi</t>
@@ -2149,7 +2149,7 @@
     <t>Future Present Past</t>
   </si>
   <si>
-    <t>Indie Rock, Post-Punk Revival</t>
+    <t>Indie Rock, Post Punk Revival</t>
   </si>
   <si>
     <t>1989 (Taylor's Version)</t>
@@ -2377,7 +2377,7 @@
     <t>Tears For Fears</t>
   </si>
   <si>
-    <t>New Wave, Pop/Rock</t>
+    <t>New Wave, Pop Rock</t>
   </si>
   <si>
     <t>Los Abuelos De La Nada 1</t>
@@ -2428,7 +2428,7 @@
     <t>LP</t>
   </si>
   <si>
-    <t>Alternative/Indie, French Indie, Pop</t>
+    <t>Alternative, Indie, French Indie, Pop</t>
   </si>
   <si>
     <t>Neon Pill</t>
@@ -2488,7 +2488,7 @@
     <t>Paramore</t>
   </si>
   <si>
-    <t>Alternative Rock, Post-Punk</t>
+    <t>Alternative Rock, Post Punk</t>
   </si>
   <si>
     <t>Listen</t>
@@ -2545,7 +2545,7 @@
     <t>I Monster</t>
   </si>
   <si>
-    <t>Alternative/Indie, Pop, Rock, French Indie</t>
+    <t>Alternative, Indie, Pop, Rock, French Indie</t>
   </si>
   <si>
     <t>Strictly 4 My N.I.G.G.A.Z...</t>
@@ -2593,7 +2593,7 @@
     <t>Neveroddoreven</t>
   </si>
   <si>
-    <t>Alternative/Indie, Electronic, Dance</t>
+    <t>Alternative, Indie, Electronic, Dance</t>
   </si>
   <si>
     <t>7,75</t>
@@ -2716,7 +2716,7 @@
     <t>shego</t>
   </si>
   <si>
-    <t>Alternative/Indie, Argentinean Rock, Spanish Rock</t>
+    <t>Alternative, Indie, Argentinean Rock, Spanish Rock</t>
   </si>
   <si>
     <t>Right Place, Wrong Person</t>
@@ -2794,7 +2794,7 @@
     <t>El Poeta Halley</t>
   </si>
   <si>
-    <t>Indie Rock, Indie Pop, Pop/Rock</t>
+    <t>Indie Rock, Indie Pop, Pop Rock</t>
   </si>
   <si>
     <t>viagr aboys</t>
@@ -2803,7 +2803,7 @@
     <t>Viagra Boys</t>
   </si>
   <si>
-    <t>Post-Punk, Psychedelic Rock, Alternative/Indie</t>
+    <t>Post Punk, Psychedelic Rock, Alternative, Indie</t>
   </si>
   <si>
     <t>Ballonerism</t>
@@ -2821,7 +2821,7 @@
     <t>Hinds</t>
   </si>
   <si>
-    <t>Alternative/Indie, Garage Rock, Indie Rock</t>
+    <t>Alternative, Indie, Garage Rock, Indie Rock</t>
   </si>
   <si>
     <t>English/Spanish</t>
@@ -2833,7 +2833,7 @@
     <t>The Temper Trap</t>
   </si>
   <si>
-    <t>Alternative/Indie, Rock, French Indie, Thai Indie</t>
+    <t>Alternative, Indie, Rock, French Indie, Thai Indie</t>
   </si>
   <si>
     <t>Speaking In Tongues</t>
@@ -2917,7 +2917,7 @@
     <t>la lune</t>
   </si>
   <si>
-    <t>Alternative/Indie, Shoegaze</t>
+    <t>Alternative, Indie, Shoegaze</t>
   </si>
   <si>
     <t>Devuélveme Las Piernas</t>
@@ -2992,7 +2992,7 @@
     <t>Joy Division</t>
   </si>
   <si>
-    <t>Alternative/Indie, Rock, Heavy Metal</t>
+    <t>Alternative, Indie, Rock, Heavy Metal</t>
   </si>
   <si>
     <t>Presente</t>
@@ -3010,13 +3010,13 @@
     <t>Dire Straits</t>
   </si>
   <si>
-    <t>Pop/Rock, Rock&amp;Roll</t>
+    <t>Pop Rock, Rock&amp;Roll</t>
   </si>
   <si>
     <t>Scaled And Icy</t>
   </si>
   <si>
-    <t>Alternative/Indie, Pop, Electronic Pop</t>
+    <t>Alternative, Indie, Pop, Electronic Pop</t>
   </si>
   <si>
     <t>Trench</t>
@@ -3028,7 +3028,7 @@
     <t>Vessel</t>
   </si>
   <si>
-    <t>Alternative/Indie, Electronic Rap, Electronic Pop</t>
+    <t>Alternative, Indie, Electronic Rap, Electronic Pop</t>
   </si>
   <si>
     <t>In the Aeroplane Over the Sea</t>
@@ -3043,7 +3043,7 @@
     <t>Tusk</t>
   </si>
   <si>
-    <t>Rock&amp;Roll, Pop/Rock, Avant Pop</t>
+    <t>Rock&amp;Roll, Pop Rock, Avant Pop</t>
   </si>
   <si>
     <t>Ese Hijo de Puta Se Mete Vidrio</t>
@@ -3052,7 +3052,7 @@
     <t>Mi Mochila Huele A Semen</t>
   </si>
   <si>
-    <t>Pop/Rock, Ambient, New Age, Prog Rock</t>
+    <t>Pop Rock, Ambient, New Age, Prog Rock</t>
   </si>
   <si>
     <t>Chet Baker Sings</t>
@@ -3070,7 +3070,7 @@
     <t>French Police</t>
   </si>
   <si>
-    <t>Alternative/Indie, French Indie, Post-Punk</t>
+    <t>Alternative, Indie, French Indie, Post Punk</t>
   </si>
   <si>
     <t>Spanish/English</t>
@@ -3118,7 +3118,7 @@
     <t>Arc</t>
   </si>
   <si>
-    <t>Alternative/Indie, Art Rock, Electronic Rock</t>
+    <t>Alternative, Indie, Art Rock, Electronic Rock</t>
   </si>
   <si>
     <t>7.</t>
@@ -3226,7 +3226,7 @@
     <t>moisturizer</t>
   </si>
   <si>
-    <t>Indie Rock, New Wave, Post-Punk, Power Pop</t>
+    <t>Indie Rock, New Wave, Post Punk, Power Pop</t>
   </si>
   <si>
     <t>THE E.N.D (THE ENERGY NEVER DIES)</t>
@@ -3283,13 +3283,13 @@
     <t>Posse EP Volume 1</t>
   </si>
   <si>
-    <t>Alternative/Indie, Electronic, Rock</t>
+    <t>Alternative, Indie, Electronic, Rock</t>
   </si>
   <si>
     <t>Rocket</t>
   </si>
   <si>
-    <t>Alternative/Indie, Indie Rock, Indie R&amp;B</t>
+    <t>Alternative, Indie, Indie Rock, Indie R&amp;B</t>
   </si>
   <si>
     <t>Fibra De Carbono</t>
@@ -3334,7 +3334,7 @@
     <t>The Hails</t>
   </si>
   <si>
-    <t>Alternative/Indie, French Indie, Alternative Rock</t>
+    <t>Alternative, Indie, French Indie, Alternative Rock</t>
   </si>
   <si>
     <t>luna park</t>
@@ -3367,7 +3367,7 @@
     <t>sombr</t>
   </si>
   <si>
-    <t>Alternative/Indie, Pop, Indie Rock</t>
+    <t>Alternative, Indie, Pop, Indie Rock</t>
   </si>
   <si>
     <t>No Rain, No Flowers</t>
@@ -3451,7 +3451,7 @@
     <t>NEIL FRANCES</t>
   </si>
   <si>
-    <t>Alternative/Indie, Dance, Electronic, Chillwave, Pop</t>
+    <t>Alternative, Indie, Dance, Electronic, Chillwave, Pop</t>
   </si>
   <si>
     <t>The Favors</t>
@@ -3580,7 +3580,7 @@
     <t>Interpol</t>
   </si>
   <si>
-    <t>Indie Rock, Post-Punk Revival, Alternative Rock</t>
+    <t>Indie Rock, Post Punk Revival, Alternative Rock</t>
   </si>
   <si>
     <t>In Your Face!</t>
@@ -3598,7 +3598,7 @@
     <t>GLU</t>
   </si>
   <si>
-    <t>Alternative/Indie, French Indie</t>
+    <t>Alternative, Indie, French Indie</t>
   </si>
   <si>
     <t>onion</t>
@@ -3637,7 +3637,7 @@
     <t>Calle Para Siempre</t>
   </si>
   <si>
-    <t>National Pop/Rock, Indie Rock, Garage Rock</t>
+    <t>National Pop Rock, Indie Rock, Garage Rock</t>
   </si>
   <si>
     <t>INSIDE</t>
@@ -3673,13 +3673,13 @@
     <t>el diablo de shanghai</t>
   </si>
   <si>
-    <t>Garage Rock, Post-Punk, Underground Rock</t>
+    <t>Garage Rock, Post Punk, Underground Rock</t>
   </si>
   <si>
     <t>Pony Pool Club</t>
   </si>
   <si>
-    <t>Post-Punk, Synth-Pop, Power Pop</t>
+    <t>Post Punk, Synth-Pop, Power Pop</t>
   </si>
   <si>
     <t>Cuando Te Muerdes el Labio</t>
@@ -3688,7 +3688,7 @@
     <t>Leiva</t>
   </si>
   <si>
-    <t>Alternative/Indie, Argentinean Rock, Rock</t>
+    <t>Alternative, Indie, Argentinean Rock, Rock</t>
   </si>
   <si>
     <t>Indie Pop, Pop, Rock, Punk</t>
@@ -3730,7 +3730,7 @@
     <t>Ginebras</t>
   </si>
   <si>
-    <t>Alternative/Indie, Rock, Argentinean Rock</t>
+    <t>Alternative, Indie, Rock, Argentinean Rock</t>
   </si>
   <si>
     <t>Circles</t>
@@ -3754,7 +3754,7 @@
     <t>Testamento</t>
   </si>
   <si>
-    <t>Indie Rock, Alternative/Indie, Spanish Rock</t>
+    <t>Indie Rock, Alternative, Indie, Spanish Rock</t>
   </si>
   <si>
     <t>Reachin' (A New Refutation Of Time And Space)</t>
@@ -4046,6 +4046,18 @@
   </si>
   <si>
     <t>R&amp;B, Hiphop</t>
+  </si>
+  <si>
+    <t>Dogrel</t>
+  </si>
+  <si>
+    <t>Fontaines D.C</t>
+  </si>
+  <si>
+    <t>Post Punk, Post Punk Revival, Indie Rock</t>
+  </si>
+  <si>
+    <t>English, Irish</t>
   </si>
 </sst>
 </file>
@@ -8734,7 +8746,7 @@
       <c r="C100" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="D100" s="15" t="s">
+      <c r="D100" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E100" s="15" t="s">
@@ -9336,8 +9348,8 @@
       <c r="C114" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="D114" s="15" t="s">
-        <v>35</v>
+      <c r="D114" s="13" t="s">
+        <v>262</v>
       </c>
       <c r="E114" s="15" t="s">
         <v>11</v>
@@ -9371,7 +9383,7 @@
     </row>
     <row r="115">
       <c r="A115" s="14" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B115" s="15" t="s">
         <v>217</v>
@@ -9414,10 +9426,10 @@
     </row>
     <row r="116">
       <c r="A116" s="14" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B116" s="15" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C116" s="15" t="s">
         <v>25</v>
@@ -9457,16 +9469,16 @@
     </row>
     <row r="117">
       <c r="A117" s="14" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B117" s="15" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C117" s="15" t="s">
         <v>9</v>
       </c>
       <c r="D117" s="15" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E117" s="15" t="s">
         <v>62</v>
@@ -9500,16 +9512,16 @@
     </row>
     <row r="118">
       <c r="A118" s="14" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B118" s="15" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C118" s="15" t="s">
         <v>25</v>
       </c>
       <c r="D118" s="15" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E118" s="15" t="s">
         <v>11</v>
@@ -9543,16 +9555,16 @@
     </row>
     <row r="119">
       <c r="A119" s="14" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B119" s="15" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C119" s="15" t="s">
         <v>9</v>
       </c>
       <c r="D119" s="15" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E119" s="15" t="s">
         <v>11</v>
@@ -9586,16 +9598,16 @@
     </row>
     <row r="120">
       <c r="A120" s="14" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B120" s="15" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C120" s="15" t="s">
         <v>9</v>
       </c>
       <c r="D120" s="15" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E120" s="15" t="s">
         <v>11</v>
@@ -9629,16 +9641,16 @@
     </row>
     <row r="121">
       <c r="A121" s="14" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B121" s="15" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C121" s="15" t="s">
         <v>9</v>
       </c>
       <c r="D121" s="15" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E121" s="15" t="s">
         <v>11</v>
@@ -9672,16 +9684,16 @@
     </row>
     <row r="122">
       <c r="A122" s="14" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B122" s="15" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C122" s="15" t="s">
         <v>9</v>
       </c>
       <c r="D122" s="15" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E122" s="15" t="s">
         <v>62</v>
@@ -9715,16 +9727,16 @@
     </row>
     <row r="123">
       <c r="A123" s="20" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B123" s="15" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C123" s="15" t="s">
         <v>9</v>
       </c>
       <c r="D123" s="15" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="E123" s="15" t="s">
         <v>62</v>
@@ -9758,10 +9770,10 @@
     </row>
     <row r="124">
       <c r="A124" s="14" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B124" s="15" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C124" s="15" t="s">
         <v>9</v>
@@ -9801,16 +9813,16 @@
     </row>
     <row r="125">
       <c r="A125" s="14" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B125" s="15" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C125" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="D125" s="15" t="s">
-        <v>290</v>
+      <c r="D125" s="13" t="s">
+        <v>291</v>
       </c>
       <c r="E125" s="15" t="s">
         <v>11</v>
@@ -9844,7 +9856,7 @@
     </row>
     <row r="126">
       <c r="A126" s="14" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B126" s="15" t="s">
         <v>44</v>
@@ -9887,10 +9899,10 @@
     </row>
     <row r="127">
       <c r="A127" s="14" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B127" s="15" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C127" s="15" t="s">
         <v>9</v>
@@ -9930,7 +9942,7 @@
     </row>
     <row r="128">
       <c r="A128" s="15" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B128" s="15" t="s">
         <v>44</v>
@@ -9939,7 +9951,7 @@
         <v>9</v>
       </c>
       <c r="D128" s="15" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E128" s="15" t="s">
         <v>11</v>
@@ -9973,16 +9985,16 @@
     </row>
     <row r="129">
       <c r="A129" s="15" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B129" s="15" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C129" s="15" t="s">
         <v>9</v>
       </c>
       <c r="D129" s="15" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E129" s="15" t="s">
         <v>11</v>
@@ -10016,16 +10028,16 @@
     </row>
     <row r="130">
       <c r="A130" s="14" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B130" s="15" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C130" s="15" t="s">
         <v>9</v>
       </c>
       <c r="D130" s="15" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E130" s="15" t="s">
         <v>62</v>
@@ -10059,7 +10071,7 @@
     </row>
     <row r="131">
       <c r="A131" s="14" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B131" s="15" t="s">
         <v>136</v>
@@ -10102,10 +10114,10 @@
     </row>
     <row r="132">
       <c r="A132" s="14" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B132" s="15" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C132" s="15" t="s">
         <v>9</v>
@@ -10145,16 +10157,16 @@
     </row>
     <row r="133">
       <c r="A133" s="14" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B133" s="15" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C133" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="D133" s="15" t="s">
-        <v>307</v>
+      <c r="D133" s="13" t="s">
+        <v>308</v>
       </c>
       <c r="E133" s="15" t="s">
         <v>11</v>
@@ -10188,16 +10200,16 @@
     </row>
     <row r="134">
       <c r="A134" s="14" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B134" s="15" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C134" s="15" t="s">
         <v>9</v>
       </c>
       <c r="D134" s="15" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E134" s="15" t="s">
         <v>11</v>
@@ -10231,16 +10243,16 @@
     </row>
     <row r="135">
       <c r="A135" s="14" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B135" s="15" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C135" s="15" t="s">
         <v>9</v>
       </c>
       <c r="D135" s="15" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E135" s="15" t="s">
         <v>11</v>
@@ -10274,16 +10286,16 @@
     </row>
     <row r="136">
       <c r="A136" s="14" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B136" s="15" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C136" s="15" t="s">
         <v>9</v>
       </c>
       <c r="D136" s="15" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E136" s="15" t="s">
         <v>11</v>
@@ -10317,19 +10329,19 @@
     </row>
     <row r="137">
       <c r="A137" s="15" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B137" s="15" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C137" s="15" t="s">
         <v>9</v>
       </c>
       <c r="D137" s="15" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="E137" s="15" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F137" s="11">
         <v>2021.0</v>
@@ -10360,16 +10372,16 @@
     </row>
     <row r="138">
       <c r="A138" s="15" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B138" s="15" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C138" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="D138" s="15" t="s">
-        <v>322</v>
+      <c r="D138" s="13" t="s">
+        <v>323</v>
       </c>
       <c r="E138" s="15" t="s">
         <v>62</v>
@@ -10403,7 +10415,7 @@
     </row>
     <row r="139">
       <c r="A139" s="15" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B139" s="15" t="s">
         <v>246</v>
@@ -10446,16 +10458,16 @@
     </row>
     <row r="140">
       <c r="A140" s="15" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B140" s="15" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C140" s="15" t="s">
         <v>9</v>
       </c>
       <c r="D140" s="15" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E140" s="15" t="s">
         <v>11</v>
@@ -10489,7 +10501,7 @@
     </row>
     <row r="141">
       <c r="A141" s="15" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B141" s="15" t="s">
         <v>77</v>
@@ -10497,8 +10509,8 @@
       <c r="C141" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="D141" s="15" t="s">
-        <v>328</v>
+      <c r="D141" s="13" t="s">
+        <v>329</v>
       </c>
       <c r="E141" s="15" t="s">
         <v>11</v>
@@ -10532,10 +10544,10 @@
     </row>
     <row r="142">
       <c r="A142" s="15" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B142" s="15" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C142" s="15" t="s">
         <v>9</v>
@@ -10575,7 +10587,7 @@
     </row>
     <row r="143">
       <c r="A143" s="15" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B143" s="15" t="s">
         <v>121</v>
@@ -10618,7 +10630,7 @@
     </row>
     <row r="144">
       <c r="A144" s="15" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B144" s="15" t="s">
         <v>246</v>
@@ -10661,7 +10673,7 @@
     </row>
     <row r="145">
       <c r="A145" s="15" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B145" s="15" t="s">
         <v>246</v>
@@ -10704,16 +10716,16 @@
     </row>
     <row r="146">
       <c r="A146" s="15" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B146" s="15" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C146" s="15" t="s">
         <v>9</v>
       </c>
       <c r="D146" s="15" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E146" s="15" t="s">
         <v>11</v>
@@ -10747,16 +10759,16 @@
     </row>
     <row r="147">
       <c r="A147" s="15" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B147" s="15" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C147" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="D147" s="15" t="s">
-        <v>339</v>
+      <c r="D147" s="13" t="s">
+        <v>340</v>
       </c>
       <c r="E147" s="15" t="s">
         <v>11</v>
@@ -10790,16 +10802,16 @@
     </row>
     <row r="148">
       <c r="A148" s="15" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B148" s="15" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C148" s="15" t="s">
         <v>9</v>
       </c>
       <c r="D148" s="15" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E148" s="15" t="s">
         <v>62</v>
@@ -10833,10 +10845,10 @@
     </row>
     <row r="149">
       <c r="A149" s="15" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B149" s="15" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C149" s="15" t="s">
         <v>9</v>
@@ -10876,7 +10888,7 @@
     </row>
     <row r="150">
       <c r="A150" s="15" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B150" s="15" t="s">
         <v>199</v>
@@ -10885,7 +10897,7 @@
         <v>9</v>
       </c>
       <c r="D150" s="15" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E150" s="15" t="s">
         <v>11</v>
@@ -10919,16 +10931,16 @@
     </row>
     <row r="151">
       <c r="A151" s="15" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B151" s="15" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C151" s="15" t="s">
         <v>9</v>
       </c>
       <c r="D151" s="15" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="E151" s="15" t="s">
         <v>11</v>
@@ -10962,16 +10974,16 @@
     </row>
     <row r="152">
       <c r="A152" s="15" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B152" s="15" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C152" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="D152" s="15" t="s">
-        <v>351</v>
+      <c r="D152" s="13" t="s">
+        <v>352</v>
       </c>
       <c r="E152" s="15" t="s">
         <v>62</v>
@@ -11005,16 +11017,16 @@
     </row>
     <row r="153">
       <c r="A153" s="15" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B153" s="15" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C153" s="15" t="s">
         <v>9</v>
       </c>
       <c r="D153" s="15" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E153" s="15" t="s">
         <v>11</v>
@@ -11048,16 +11060,16 @@
     </row>
     <row r="154">
       <c r="A154" s="15" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B154" s="15" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C154" s="15" t="s">
         <v>9</v>
       </c>
       <c r="D154" s="15" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="E154" s="15" t="s">
         <v>11</v>
@@ -11066,7 +11078,7 @@
         <v>1982.0</v>
       </c>
       <c r="G154" s="16" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H154" s="15"/>
       <c r="I154" s="13"/>
@@ -11091,16 +11103,16 @@
     </row>
     <row r="155">
       <c r="A155" s="15" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B155" s="15" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C155" s="15" t="s">
         <v>9</v>
       </c>
       <c r="D155" s="15" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E155" s="15" t="s">
         <v>11</v>
@@ -11134,16 +11146,16 @@
     </row>
     <row r="156">
       <c r="A156" s="15" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B156" s="15" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C156" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="D156" s="15" t="s">
-        <v>364</v>
+      <c r="D156" s="13" t="s">
+        <v>365</v>
       </c>
       <c r="E156" s="15" t="s">
         <v>11</v>
@@ -11177,10 +11189,10 @@
     </row>
     <row r="157">
       <c r="A157" s="15" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B157" s="15" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C157" s="15" t="s">
         <v>9</v>
@@ -11220,16 +11232,16 @@
     </row>
     <row r="158">
       <c r="A158" s="15" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B158" s="15" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C158" s="15" t="s">
         <v>9</v>
       </c>
       <c r="D158" s="15" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E158" s="15" t="s">
         <v>11</v>
@@ -11263,10 +11275,10 @@
     </row>
     <row r="159">
       <c r="A159" s="15" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B159" s="15" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C159" s="15" t="s">
         <v>9</v>
@@ -11306,16 +11318,16 @@
     </row>
     <row r="160">
       <c r="A160" s="15" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B160" s="15" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C160" s="15" t="s">
         <v>9</v>
       </c>
       <c r="D160" s="15" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="E160" s="15" t="s">
         <v>11</v>
@@ -11349,16 +11361,16 @@
     </row>
     <row r="161">
       <c r="A161" s="15" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B161" s="15" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C161" s="15" t="s">
         <v>9</v>
       </c>
       <c r="D161" s="15" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="E161" s="15" t="s">
         <v>11</v>
@@ -11392,16 +11404,16 @@
     </row>
     <row r="162">
       <c r="A162" s="15" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B162" s="13" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C162" s="15" t="s">
         <v>9</v>
       </c>
       <c r="D162" s="15" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E162" s="15" t="s">
         <v>11</v>
@@ -11435,16 +11447,16 @@
     </row>
     <row r="163">
       <c r="A163" s="15" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B163" s="13" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C163" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="D163" s="15" t="s">
-        <v>382</v>
+      <c r="D163" s="13" t="s">
+        <v>383</v>
       </c>
       <c r="E163" s="15" t="s">
         <v>62</v>
@@ -11478,16 +11490,16 @@
     </row>
     <row r="164">
       <c r="A164" s="15" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B164" s="15" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C164" s="15" t="s">
         <v>9</v>
       </c>
       <c r="D164" s="15" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E164" s="15" t="s">
         <v>11</v>
@@ -11521,16 +11533,16 @@
     </row>
     <row r="165">
       <c r="A165" s="15" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B165" s="15" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C165" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="D165" s="15" t="s">
-        <v>388</v>
+      <c r="D165" s="13" t="s">
+        <v>389</v>
       </c>
       <c r="E165" s="15" t="s">
         <v>11</v>
@@ -11564,19 +11576,19 @@
     </row>
     <row r="166">
       <c r="A166" s="15" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B166" s="15" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C166" s="15" t="s">
         <v>25</v>
       </c>
       <c r="D166" s="15" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="E166" s="15" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F166" s="11">
         <v>2024.0</v>
@@ -11607,16 +11619,16 @@
     </row>
     <row r="167">
       <c r="A167" s="15" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B167" s="15" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C167" s="15" t="s">
         <v>9</v>
       </c>
       <c r="D167" s="15" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="E167" s="15" t="s">
         <v>11</v>
@@ -11650,16 +11662,16 @@
     </row>
     <row r="168">
       <c r="A168" s="15" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B168" s="15" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C168" s="15" t="s">
         <v>9</v>
       </c>
       <c r="D168" s="15" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="E168" s="15" t="s">
         <v>11</v>
@@ -11693,16 +11705,16 @@
     </row>
     <row r="169">
       <c r="A169" s="15" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B169" s="15" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C169" s="15" t="s">
         <v>9</v>
       </c>
       <c r="D169" s="15" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="E169" s="15" t="s">
         <v>11</v>
@@ -11736,16 +11748,16 @@
     </row>
     <row r="170">
       <c r="A170" s="15" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B170" s="15" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C170" s="15" t="s">
         <v>9</v>
       </c>
       <c r="D170" s="13" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="E170" s="15" t="s">
         <v>11</v>
@@ -11779,7 +11791,7 @@
     </row>
     <row r="171">
       <c r="A171" s="15" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B171" s="15" t="s">
         <v>112</v>
@@ -11822,16 +11834,16 @@
     </row>
     <row r="172">
       <c r="A172" s="15" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B172" s="15" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C172" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="D172" s="15" t="s">
-        <v>388</v>
+      <c r="D172" s="13" t="s">
+        <v>389</v>
       </c>
       <c r="E172" s="15" t="s">
         <v>11</v>
@@ -11865,16 +11877,16 @@
     </row>
     <row r="173">
       <c r="A173" s="15" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B173" s="15" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C173" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="D173" s="15" t="s">
-        <v>408</v>
+      <c r="D173" s="13" t="s">
+        <v>409</v>
       </c>
       <c r="E173" s="15" t="s">
         <v>62</v>
@@ -11908,19 +11920,19 @@
     </row>
     <row r="174">
       <c r="A174" s="15" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B174" s="15" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C174" s="15" t="s">
         <v>9</v>
       </c>
       <c r="D174" s="15" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="E174" s="15" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F174" s="11">
         <v>2015.0</v>
@@ -11951,7 +11963,7 @@
     </row>
     <row r="175">
       <c r="A175" s="15" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B175" s="15" t="s">
         <v>20</v>
@@ -11994,16 +12006,16 @@
     </row>
     <row r="176">
       <c r="A176" s="15" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B176" s="15" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C176" s="15" t="s">
         <v>9</v>
       </c>
       <c r="D176" s="15" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E176" s="15" t="s">
         <v>11</v>
@@ -12037,15 +12049,15 @@
     </row>
     <row r="177">
       <c r="A177" s="15" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B177" s="15" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C177" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="D177" s="15" t="s">
+      <c r="D177" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E177" s="15" t="s">
@@ -12080,16 +12092,16 @@
     </row>
     <row r="178">
       <c r="A178" s="15" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B178" s="15" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C178" s="15" t="s">
         <v>9</v>
       </c>
       <c r="D178" s="15" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E178" s="15" t="s">
         <v>62</v>
@@ -12123,16 +12135,16 @@
     </row>
     <row r="179">
       <c r="A179" s="15" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B179" s="15" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C179" s="15" t="s">
         <v>9</v>
       </c>
       <c r="D179" s="15" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E179" s="15" t="s">
         <v>11</v>
@@ -12166,16 +12178,16 @@
     </row>
     <row r="180">
       <c r="A180" s="15" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B180" s="15" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C180" s="15" t="s">
         <v>143</v>
       </c>
       <c r="D180" s="15" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E180" s="15" t="s">
         <v>11</v>
@@ -12209,16 +12221,16 @@
     </row>
     <row r="181">
       <c r="A181" s="13" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B181" s="15" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C181" s="15" t="s">
         <v>9</v>
       </c>
       <c r="D181" s="15" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="E181" s="15" t="s">
         <v>11</v>
@@ -12252,16 +12264,16 @@
     </row>
     <row r="182">
       <c r="A182" s="15" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B182" s="15" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C182" s="15" t="s">
         <v>9</v>
       </c>
       <c r="D182" s="15" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E182" s="15" t="s">
         <v>11</v>
@@ -12295,16 +12307,16 @@
     </row>
     <row r="183">
       <c r="A183" s="15" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B183" s="15" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C183" s="15" t="s">
         <v>9</v>
       </c>
       <c r="D183" s="15" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E183" s="15" t="s">
         <v>11</v>
@@ -12338,16 +12350,16 @@
     </row>
     <row r="184">
       <c r="A184" s="15" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B184" s="15" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C184" s="15" t="s">
         <v>9</v>
       </c>
       <c r="D184" s="15" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E184" s="15" t="s">
         <v>11</v>
@@ -12381,16 +12393,16 @@
     </row>
     <row r="185">
       <c r="A185" s="15" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B185" s="15" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C185" s="15" t="s">
         <v>9</v>
       </c>
       <c r="D185" s="15" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="E185" s="15" t="s">
         <v>255</v>
@@ -12424,7 +12436,7 @@
     </row>
     <row r="186">
       <c r="A186" s="15" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B186" s="15" t="s">
         <v>20</v>
@@ -12467,16 +12479,16 @@
     </row>
     <row r="187">
       <c r="A187" s="15" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B187" s="15" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C187" s="15" t="s">
         <v>9</v>
       </c>
       <c r="D187" s="15" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E187" s="15" t="s">
         <v>11</v>
@@ -12510,16 +12522,16 @@
     </row>
     <row r="188">
       <c r="A188" s="15" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B188" s="15" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C188" s="15" t="s">
         <v>9</v>
       </c>
       <c r="D188" s="15" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="E188" s="15" t="s">
         <v>11</v>
@@ -12553,19 +12565,19 @@
     </row>
     <row r="189">
       <c r="A189" s="15" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B189" s="15" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C189" s="15" t="s">
         <v>9</v>
       </c>
       <c r="D189" s="15" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="E189" s="15" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="F189" s="11">
         <v>1978.0</v>
@@ -12596,16 +12608,16 @@
     </row>
     <row r="190">
       <c r="A190" s="15" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B190" s="15" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C190" s="15" t="s">
         <v>9</v>
       </c>
       <c r="D190" s="15" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="E190" s="15" t="s">
         <v>11</v>
@@ -12639,7 +12651,7 @@
     </row>
     <row r="191">
       <c r="A191" s="15" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B191" s="15" t="s">
         <v>71</v>
@@ -12648,7 +12660,7 @@
         <v>9</v>
       </c>
       <c r="D191" s="15" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="E191" s="15" t="s">
         <v>11</v>
@@ -12682,7 +12694,7 @@
     </row>
     <row r="192">
       <c r="A192" s="15" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B192" s="15" t="s">
         <v>20</v>
@@ -12691,7 +12703,7 @@
         <v>25</v>
       </c>
       <c r="D192" s="15" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E192" s="15" t="s">
         <v>11</v>
@@ -12725,7 +12737,7 @@
     </row>
     <row r="193">
       <c r="A193" s="15" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B193" s="15" t="s">
         <v>20</v>
@@ -12734,7 +12746,7 @@
         <v>25</v>
       </c>
       <c r="D193" s="15" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E193" s="15" t="s">
         <v>11</v>
@@ -12768,7 +12780,7 @@
     </row>
     <row r="194">
       <c r="A194" s="15" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B194" s="15" t="s">
         <v>20</v>
@@ -12777,7 +12789,7 @@
         <v>25</v>
       </c>
       <c r="D194" s="15" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E194" s="15" t="s">
         <v>11</v>
@@ -12811,16 +12823,16 @@
     </row>
     <row r="195">
       <c r="A195" s="15" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B195" s="15" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C195" s="15" t="s">
         <v>9</v>
       </c>
       <c r="D195" s="15" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="E195" s="15" t="s">
         <v>11</v>
@@ -12854,16 +12866,16 @@
     </row>
     <row r="196">
       <c r="A196" s="15" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B196" s="15" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C196" s="15" t="s">
         <v>9</v>
       </c>
       <c r="D196" s="15" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="E196" s="15" t="s">
         <v>11</v>
@@ -12897,16 +12909,16 @@
     </row>
     <row r="197">
       <c r="A197" s="15" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B197" s="15" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C197" s="15" t="s">
         <v>9</v>
       </c>
       <c r="D197" s="15" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E197" s="15" t="s">
         <v>11</v>
@@ -12940,16 +12952,16 @@
     </row>
     <row r="198">
       <c r="A198" s="15" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B198" s="15" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C198" s="15" t="s">
         <v>9</v>
       </c>
       <c r="D198" s="15" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="E198" s="15" t="s">
         <v>62</v>
@@ -12983,7 +12995,7 @@
     </row>
     <row r="199">
       <c r="A199" s="15" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B199" s="15" t="s">
         <v>163</v>
@@ -12992,7 +13004,7 @@
         <v>9</v>
       </c>
       <c r="D199" s="13" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="E199" s="15" t="s">
         <v>11</v>
@@ -13026,16 +13038,16 @@
     </row>
     <row r="200">
       <c r="A200" s="15" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B200" s="15" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C200" s="15" t="s">
         <v>9</v>
       </c>
       <c r="D200" s="15" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="E200" s="15" t="s">
         <v>11</v>
@@ -13069,7 +13081,7 @@
     </row>
     <row r="201">
       <c r="A201" s="15" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B201" s="15" t="s">
         <v>199</v>
@@ -13112,16 +13124,16 @@
     </row>
     <row r="202">
       <c r="A202" s="15" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B202" s="15" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C202" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="D202" s="15" t="s">
-        <v>473</v>
+      <c r="D202" s="13" t="s">
+        <v>474</v>
       </c>
       <c r="E202" s="15" t="s">
         <v>11</v>
@@ -13155,16 +13167,16 @@
     </row>
     <row r="203">
       <c r="A203" s="15" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B203" s="15" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C203" s="15" t="s">
         <v>9</v>
       </c>
       <c r="D203" s="15" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="E203" s="15" t="s">
         <v>11</v>
@@ -13173,7 +13185,7 @@
         <v>1994.0</v>
       </c>
       <c r="G203" s="16" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H203" s="15"/>
       <c r="I203" s="17"/>
@@ -13198,16 +13210,16 @@
     </row>
     <row r="204">
       <c r="A204" s="15" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B204" s="15" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C204" s="15" t="s">
         <v>9</v>
       </c>
       <c r="D204" s="15" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E204" s="15" t="s">
         <v>11</v>
@@ -13241,10 +13253,10 @@
     </row>
     <row r="205">
       <c r="A205" s="15" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B205" s="15" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C205" s="15" t="s">
         <v>9</v>
@@ -13284,16 +13296,16 @@
     </row>
     <row r="206">
       <c r="A206" s="15" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B206" s="15" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C206" s="15" t="s">
         <v>9</v>
       </c>
       <c r="D206" s="15" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="E206" s="15" t="s">
         <v>62</v>
@@ -13327,16 +13339,16 @@
     </row>
     <row r="207">
       <c r="A207" s="15" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B207" s="15" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C207" s="15" t="s">
         <v>9</v>
       </c>
       <c r="D207" s="15" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="E207" s="15" t="s">
         <v>11</v>
@@ -13370,16 +13382,16 @@
     </row>
     <row r="208">
       <c r="A208" s="15" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B208" s="15" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C208" s="15" t="s">
         <v>9</v>
       </c>
       <c r="D208" s="15" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="E208" s="15" t="s">
         <v>11</v>
@@ -13413,7 +13425,7 @@
     </row>
     <row r="209">
       <c r="A209" s="15" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B209" s="15" t="s">
         <v>24</v>
@@ -13422,7 +13434,7 @@
         <v>9</v>
       </c>
       <c r="D209" s="15" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="E209" s="15" t="s">
         <v>11</v>
@@ -13456,15 +13468,15 @@
     </row>
     <row r="210">
       <c r="A210" s="15" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B210" s="15" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C210" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="D210" s="15" t="s">
+      <c r="D210" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E210" s="15" t="s">
@@ -13499,16 +13511,16 @@
     </row>
     <row r="211">
       <c r="A211" s="15" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B211" s="15" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C211" s="15" t="s">
         <v>9</v>
       </c>
       <c r="D211" s="15" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="E211" s="15" t="s">
         <v>62</v>
@@ -13542,16 +13554,16 @@
     </row>
     <row r="212">
       <c r="A212" s="15" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B212" s="15" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C212" s="15" t="s">
         <v>9</v>
       </c>
       <c r="D212" s="15" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="E212" s="15" t="s">
         <v>11</v>
@@ -13585,16 +13597,16 @@
     </row>
     <row r="213">
       <c r="A213" s="15" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B213" s="15" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C213" s="15" t="s">
         <v>9</v>
       </c>
       <c r="D213" s="15" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="E213" s="15" t="s">
         <v>11</v>
@@ -13603,7 +13615,7 @@
         <v>2024.0</v>
       </c>
       <c r="G213" s="16" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H213" s="15"/>
       <c r="I213" s="17"/>
@@ -13628,16 +13640,16 @@
     </row>
     <row r="214">
       <c r="A214" s="15" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B214" s="15" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C214" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="D214" s="15" t="s">
-        <v>503</v>
+      <c r="D214" s="13" t="s">
+        <v>504</v>
       </c>
       <c r="E214" s="15" t="s">
         <v>11</v>
@@ -13671,10 +13683,10 @@
     </row>
     <row r="215">
       <c r="A215" s="15" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B215" s="15" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C215" s="15" t="s">
         <v>9</v>
@@ -13689,7 +13701,7 @@
         <v>2009.0</v>
       </c>
       <c r="G215" s="16" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H215" s="15"/>
       <c r="I215" s="17"/>
@@ -13714,16 +13726,16 @@
     </row>
     <row r="216">
       <c r="A216" s="15" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B216" s="15" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C216" s="15" t="s">
         <v>9</v>
       </c>
       <c r="D216" s="15" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="E216" s="15" t="s">
         <v>11</v>
@@ -13757,16 +13769,16 @@
     </row>
     <row r="217">
       <c r="A217" s="15" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B217" s="15" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C217" s="15" t="s">
         <v>9</v>
       </c>
       <c r="D217" s="15" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E217" s="15" t="s">
         <v>11</v>
@@ -13800,16 +13812,16 @@
     </row>
     <row r="218">
       <c r="A218" s="15" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B218" s="15" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C218" s="15" t="s">
         <v>143</v>
       </c>
       <c r="D218" s="15" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="E218" s="15" t="s">
         <v>11</v>
@@ -13843,7 +13855,7 @@
     </row>
     <row r="219">
       <c r="A219" s="15" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B219" s="15" t="s">
         <v>199</v>
@@ -13886,16 +13898,16 @@
     </row>
     <row r="220">
       <c r="A220" s="15" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B220" s="15" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C220" s="15" t="s">
         <v>9</v>
       </c>
       <c r="D220" s="15" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="E220" s="15" t="s">
         <v>11</v>
@@ -13904,7 +13916,7 @@
         <v>2016.0</v>
       </c>
       <c r="G220" s="16" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H220" s="15"/>
       <c r="I220" s="17"/>
@@ -13929,16 +13941,16 @@
     </row>
     <row r="221">
       <c r="A221" s="15" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B221" s="15" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C221" s="15" t="s">
         <v>25</v>
       </c>
       <c r="D221" s="15" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="E221" s="15" t="s">
         <v>11</v>
@@ -13972,16 +13984,16 @@
     </row>
     <row r="222">
       <c r="A222" s="15" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B222" s="15" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C222" s="15" t="s">
         <v>25</v>
       </c>
       <c r="D222" s="15" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="E222" s="15" t="s">
         <v>11</v>
@@ -14015,16 +14027,16 @@
     </row>
     <row r="223">
       <c r="A223" s="15" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B223" s="15" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C223" s="15" t="s">
         <v>9</v>
       </c>
       <c r="D223" s="15" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="E223" s="15" t="s">
         <v>11</v>
@@ -14058,16 +14070,16 @@
     </row>
     <row r="224">
       <c r="A224" s="15" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B224" s="15" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C224" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="D224" s="15" t="s">
-        <v>524</v>
+      <c r="D224" s="13" t="s">
+        <v>525</v>
       </c>
       <c r="E224" s="15" t="s">
         <v>11</v>
@@ -14101,16 +14113,16 @@
     </row>
     <row r="225">
       <c r="A225" s="13" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B225" s="13" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C225" s="13" t="s">
         <v>9</v>
       </c>
       <c r="D225" s="13" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="E225" s="13" t="s">
         <v>11</v>
@@ -14119,7 +14131,7 @@
         <v>2004.0</v>
       </c>
       <c r="G225" s="12" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H225" s="13"/>
       <c r="I225" s="14"/>
@@ -14144,16 +14156,16 @@
     </row>
     <row r="226">
       <c r="A226" s="15" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B226" s="15" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C226" s="15" t="s">
         <v>9</v>
       </c>
       <c r="D226" s="15" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="E226" s="15" t="s">
         <v>11</v>
@@ -14187,16 +14199,16 @@
     </row>
     <row r="227">
       <c r="A227" s="15" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B227" s="15" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C227" s="15" t="s">
         <v>9</v>
       </c>
       <c r="D227" s="15" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="E227" s="15" t="s">
         <v>11</v>
@@ -14205,7 +14217,7 @@
         <v>1998.0</v>
       </c>
       <c r="G227" s="16" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H227" s="15"/>
       <c r="I227" s="17"/>
@@ -14230,16 +14242,16 @@
     </row>
     <row r="228">
       <c r="A228" s="15" t="s">
+        <v>534</v>
+      </c>
+      <c r="B228" s="15" t="s">
+        <v>535</v>
+      </c>
+      <c r="C228" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="D228" s="15" t="s">
         <v>533</v>
-      </c>
-      <c r="B228" s="15" t="s">
-        <v>534</v>
-      </c>
-      <c r="C228" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="D228" s="15" t="s">
-        <v>532</v>
       </c>
       <c r="E228" s="15" t="s">
         <v>11</v>
@@ -14273,7 +14285,7 @@
     </row>
     <row r="229">
       <c r="A229" s="15" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B229" s="15" t="s">
         <v>59</v>
@@ -14282,7 +14294,7 @@
         <v>9</v>
       </c>
       <c r="D229" s="15" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="E229" s="15" t="s">
         <v>11</v>
@@ -14316,16 +14328,16 @@
     </row>
     <row r="230">
       <c r="A230" s="15" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B230" s="15" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C230" s="15" t="s">
         <v>9</v>
       </c>
       <c r="D230" s="15" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="E230" s="15" t="s">
         <v>11</v>
@@ -14359,16 +14371,16 @@
     </row>
     <row r="231">
       <c r="A231" s="15" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B231" s="15" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C231" s="15" t="s">
         <v>9</v>
       </c>
       <c r="D231" s="15" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="E231" s="15" t="s">
         <v>11</v>
@@ -14402,15 +14414,15 @@
     </row>
     <row r="232">
       <c r="A232" s="15" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B232" s="15" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C232" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="D232" s="15" t="s">
+      <c r="D232" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E232" s="15" t="s">
@@ -14445,7 +14457,7 @@
     </row>
     <row r="233">
       <c r="A233" s="15" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B233" s="15" t="s">
         <v>139</v>
@@ -14454,7 +14466,7 @@
         <v>9</v>
       </c>
       <c r="D233" s="15" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="E233" s="15" t="s">
         <v>11</v>
@@ -14488,16 +14500,16 @@
     </row>
     <row r="234">
       <c r="A234" s="15" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B234" s="15" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C234" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="D234" s="15" t="s">
-        <v>548</v>
+      <c r="D234" s="13" t="s">
+        <v>549</v>
       </c>
       <c r="E234" s="15" t="s">
         <v>11</v>
@@ -14531,16 +14543,16 @@
     </row>
     <row r="235">
       <c r="A235" s="15" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B235" s="15" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C235" s="15" t="s">
         <v>9</v>
       </c>
       <c r="D235" s="15" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="E235" s="15" t="s">
         <v>11</v>
@@ -14574,16 +14586,16 @@
     </row>
     <row r="236">
       <c r="A236" s="15" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B236" s="15" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C236" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="D236" s="15" t="s">
-        <v>548</v>
+      <c r="D236" s="13" t="s">
+        <v>549</v>
       </c>
       <c r="E236" s="15" t="s">
         <v>11</v>
@@ -14617,16 +14629,16 @@
     </row>
     <row r="237">
       <c r="A237" s="15" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B237" s="13" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C237" s="15" t="s">
         <v>9</v>
       </c>
       <c r="D237" s="15" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="E237" s="15" t="s">
         <v>11</v>
@@ -14660,16 +14672,16 @@
     </row>
     <row r="238">
       <c r="A238" s="15" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B238" s="15" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C238" s="15" t="s">
         <v>9</v>
       </c>
       <c r="D238" s="15" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="E238" s="15" t="s">
         <v>11</v>
@@ -14703,16 +14715,16 @@
     </row>
     <row r="239">
       <c r="A239" s="15" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B239" s="15" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C239" s="15" t="s">
         <v>9</v>
       </c>
       <c r="D239" s="15" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="E239" s="15" t="s">
         <v>11</v>
@@ -14746,16 +14758,16 @@
     </row>
     <row r="240">
       <c r="A240" s="15" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B240" s="15" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C240" s="15" t="s">
         <v>9</v>
       </c>
       <c r="D240" s="15" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="E240" s="15" t="s">
         <v>11</v>
@@ -14789,16 +14801,16 @@
     </row>
     <row r="241">
       <c r="A241" s="15" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B241" s="15" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C241" s="15" t="s">
         <v>9</v>
       </c>
       <c r="D241" s="15" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="E241" s="15" t="s">
         <v>11</v>
@@ -14832,15 +14844,15 @@
     </row>
     <row r="242">
       <c r="A242" s="15" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B242" s="15" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C242" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="D242" s="15" t="s">
+      <c r="D242" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E242" s="15" t="s">
@@ -14875,16 +14887,16 @@
     </row>
     <row r="243">
       <c r="A243" s="15" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B243" s="15" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C243" s="15" t="s">
         <v>9</v>
       </c>
       <c r="D243" s="15" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E243" s="15" t="s">
         <v>11</v>
@@ -14918,16 +14930,16 @@
     </row>
     <row r="244">
       <c r="A244" s="15" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B244" s="15" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C244" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="D244" s="15" t="s">
-        <v>568</v>
+      <c r="D244" s="13" t="s">
+        <v>569</v>
       </c>
       <c r="E244" s="15" t="s">
         <v>11</v>
@@ -14961,16 +14973,16 @@
     </row>
     <row r="245">
       <c r="A245" s="15" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B245" s="15" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C245" s="15" t="s">
         <v>9</v>
       </c>
       <c r="D245" s="15" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="E245" s="15" t="s">
         <v>11</v>
@@ -15004,16 +15016,16 @@
     </row>
     <row r="246">
       <c r="A246" s="15" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B246" s="15" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C246" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="D246" s="15" t="s">
-        <v>574</v>
+      <c r="D246" s="13" t="s">
+        <v>575</v>
       </c>
       <c r="E246" s="15" t="s">
         <v>11</v>
@@ -15047,16 +15059,16 @@
     </row>
     <row r="247">
       <c r="A247" s="15" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B247" s="15" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C247" s="15" t="s">
         <v>9</v>
       </c>
       <c r="D247" s="15" t="s">
-        <v>576</v>
+        <v>389</v>
       </c>
       <c r="E247" s="15" t="s">
         <v>11</v>
@@ -15093,7 +15105,7 @@
         <v>577</v>
       </c>
       <c r="B248" s="15" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C248" s="15" t="s">
         <v>9</v>
@@ -15179,7 +15191,7 @@
         <v>581</v>
       </c>
       <c r="B250" s="15" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C250" s="15" t="s">
         <v>9</v>
@@ -15222,7 +15234,7 @@
         <v>583</v>
       </c>
       <c r="B251" s="15" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C251" s="15" t="s">
         <v>9</v>
@@ -15443,7 +15455,7 @@
         <v>9</v>
       </c>
       <c r="D256" s="15" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="E256" s="15" t="s">
         <v>11</v>
@@ -15529,7 +15541,7 @@
         <v>9</v>
       </c>
       <c r="D258" s="15" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E258" s="15" t="s">
         <v>62</v>
@@ -15658,7 +15670,7 @@
         <v>25</v>
       </c>
       <c r="D261" s="15" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="E261" s="15" t="s">
         <v>11</v>
@@ -15786,7 +15798,7 @@
       <c r="C264" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="D264" s="15" t="s">
+      <c r="D264" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E264" s="15" t="s">
@@ -15829,7 +15841,7 @@
       <c r="C265" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="D265" s="15" t="s">
+      <c r="D265" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E265" s="15" t="s">
@@ -15958,7 +15970,7 @@
       <c r="C268" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="D268" s="15" t="s">
+      <c r="D268" s="13" t="s">
         <v>609</v>
       </c>
       <c r="E268" s="15" t="s">
@@ -16082,7 +16094,7 @@
         <v>615</v>
       </c>
       <c r="B271" s="15" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C271" s="15" t="s">
         <v>9</v>
@@ -16431,7 +16443,7 @@
       <c r="C279" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="D279" s="15" t="s">
+      <c r="D279" s="13" t="s">
         <v>633</v>
       </c>
       <c r="E279" s="15" t="s">
@@ -16474,7 +16486,7 @@
       <c r="C280" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="D280" s="15" t="s">
+      <c r="D280" s="13" t="s">
         <v>635</v>
       </c>
       <c r="E280" s="15" t="s">
@@ -16603,7 +16615,7 @@
       <c r="C283" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="D283" s="15" t="s">
+      <c r="D283" s="13" t="s">
         <v>639</v>
       </c>
       <c r="E283" s="15" t="s">
@@ -16641,7 +16653,7 @@
         <v>640</v>
       </c>
       <c r="B284" s="15" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C284" s="15" t="s">
         <v>9</v>
@@ -16736,7 +16748,7 @@
         <v>39</v>
       </c>
       <c r="E286" s="15" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="F286" s="11">
         <v>2024.0</v>
@@ -16822,7 +16834,7 @@
         <v>653</v>
       </c>
       <c r="E288" s="15" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F288" s="11">
         <v>2019.0</v>
@@ -16861,11 +16873,11 @@
       <c r="C289" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="D289" s="15" t="s">
+      <c r="D289" s="13" t="s">
         <v>655</v>
       </c>
       <c r="E289" s="15" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F289" s="11">
         <v>2021.0</v>
@@ -16985,13 +16997,13 @@
         <v>659</v>
       </c>
       <c r="B292" s="15" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C292" s="15" t="s">
         <v>9</v>
       </c>
       <c r="D292" s="15" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E292" s="15" t="s">
         <v>11</v>
@@ -17129,7 +17141,7 @@
         <v>2000.0</v>
       </c>
       <c r="G295" s="16" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H295" s="15"/>
       <c r="I295" s="14"/>
@@ -17163,7 +17175,7 @@
         <v>9</v>
       </c>
       <c r="D296" s="15" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E296" s="15" t="s">
         <v>255</v>
@@ -17205,7 +17217,7 @@
       <c r="C297" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="D297" s="15" t="s">
+      <c r="D297" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E297" s="15" t="s">
@@ -17301,7 +17313,7 @@
         <v>2024.0</v>
       </c>
       <c r="G299" s="16" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H299" s="15"/>
       <c r="I299" s="17"/>
@@ -17463,7 +17475,7 @@
       <c r="C303" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="D303" s="15" t="s">
+      <c r="D303" s="13" t="s">
         <v>687</v>
       </c>
       <c r="E303" s="15" t="s">
@@ -17587,7 +17599,7 @@
         <v>693</v>
       </c>
       <c r="B306" s="15" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C306" s="15" t="s">
         <v>25</v>
@@ -17807,7 +17819,7 @@
       <c r="C311" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="D311" s="15" t="s">
+      <c r="D311" s="13" t="s">
         <v>704</v>
       </c>
       <c r="E311" s="15" t="s">
@@ -17931,7 +17943,7 @@
         <v>710</v>
       </c>
       <c r="B314" s="15" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C314" s="15" t="s">
         <v>9</v>
@@ -18017,7 +18029,7 @@
         <v>715</v>
       </c>
       <c r="B316" s="15" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C316" s="15" t="s">
         <v>9</v>
@@ -18060,13 +18072,13 @@
         <v>717</v>
       </c>
       <c r="B317" s="15" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C317" s="15" t="s">
         <v>9</v>
       </c>
       <c r="D317" s="15" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="E317" s="15" t="s">
         <v>11</v>
@@ -18103,7 +18115,7 @@
         <v>718</v>
       </c>
       <c r="B318" s="15" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C318" s="15" t="s">
         <v>9</v>
@@ -18146,7 +18158,7 @@
         <v>720</v>
       </c>
       <c r="B319" s="15" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C319" s="15" t="s">
         <v>9</v>
@@ -18495,7 +18507,7 @@
       <c r="C327" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="D327" s="15" t="s">
+      <c r="D327" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E327" s="15" t="s">
@@ -18539,7 +18551,7 @@
         <v>9</v>
       </c>
       <c r="D328" s="15" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E328" s="15" t="s">
         <v>62</v>
@@ -18624,7 +18636,7 @@
       <c r="C330" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="D330" s="15" t="s">
+      <c r="D330" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E330" s="15" t="s">
@@ -18667,7 +18679,7 @@
       <c r="C331" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="D331" s="15" t="s">
+      <c r="D331" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E331" s="15" t="s">
@@ -18791,7 +18803,7 @@
         <v>754</v>
       </c>
       <c r="B334" s="15" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C334" s="15" t="s">
         <v>9</v>
@@ -18925,7 +18937,7 @@
       <c r="C337" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="D337" s="15" t="s">
+      <c r="D337" s="13" t="s">
         <v>635</v>
       </c>
       <c r="E337" s="15" t="s">
@@ -19054,8 +19066,8 @@
       <c r="C340" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="D340" s="15" t="s">
-        <v>307</v>
+      <c r="D340" s="13" t="s">
+        <v>308</v>
       </c>
       <c r="E340" s="15" t="s">
         <v>62</v>
@@ -19226,7 +19238,7 @@
       <c r="C344" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="D344" s="15" t="s">
+      <c r="D344" s="13" t="s">
         <v>780</v>
       </c>
       <c r="E344" s="15" t="s">
@@ -19270,7 +19282,7 @@
         <v>9</v>
       </c>
       <c r="D345" s="15" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E345" s="15" t="s">
         <v>62</v>
@@ -19527,8 +19539,8 @@
       <c r="C351" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="D351" s="15" t="s">
-        <v>339</v>
+      <c r="D351" s="13" t="s">
+        <v>340</v>
       </c>
       <c r="E351" s="15" t="s">
         <v>62</v>
@@ -19570,7 +19582,7 @@
       <c r="C352" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="D352" s="15" t="s">
+      <c r="D352" s="13" t="s">
         <v>797</v>
       </c>
       <c r="E352" s="15" t="s">
@@ -19613,7 +19625,7 @@
       <c r="C353" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="D353" s="15" t="s">
+      <c r="D353" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E353" s="15" t="s">
@@ -19871,7 +19883,7 @@
       <c r="C359" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="D359" s="15" t="s">
+      <c r="D359" s="13" t="s">
         <v>817</v>
       </c>
       <c r="E359" s="21" t="s">
@@ -19881,7 +19893,7 @@
         <v>2023.0</v>
       </c>
       <c r="G359" s="16" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H359" s="15"/>
       <c r="I359" s="17"/>
@@ -19914,8 +19926,8 @@
       <c r="C360" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="D360" s="15" t="s">
-        <v>307</v>
+      <c r="D360" s="13" t="s">
+        <v>308</v>
       </c>
       <c r="E360" s="10" t="s">
         <v>11</v>
@@ -20010,7 +20022,7 @@
         <v>2011.0</v>
       </c>
       <c r="G362" s="16" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H362" s="15"/>
       <c r="I362" s="14"/>
@@ -20139,7 +20151,7 @@
         <v>2008.0</v>
       </c>
       <c r="G365" s="16" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H365" s="15"/>
       <c r="I365" s="14"/>
@@ -20301,7 +20313,7 @@
       <c r="C369" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="D369" s="15" t="s">
+      <c r="D369" s="13" t="s">
         <v>836</v>
       </c>
       <c r="E369" s="15" t="s">
@@ -20434,7 +20446,7 @@
         <v>845</v>
       </c>
       <c r="E372" s="15" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="F372" s="11">
         <v>1996.0</v>
@@ -20511,7 +20523,7 @@
         <v>849</v>
       </c>
       <c r="B374" s="15" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C374" s="15" t="s">
         <v>9</v>
@@ -20559,7 +20571,7 @@
       <c r="C375" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="D375" s="15" t="s">
+      <c r="D375" s="13" t="s">
         <v>852</v>
       </c>
       <c r="E375" s="15" t="s">
@@ -20649,7 +20661,7 @@
         <v>859</v>
       </c>
       <c r="E377" s="15" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="F377" s="11">
         <v>2018.0</v>
@@ -20688,8 +20700,8 @@
       <c r="C378" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="D378" s="15" t="s">
-        <v>568</v>
+      <c r="D378" s="13" t="s">
+        <v>569</v>
       </c>
       <c r="E378" s="15" t="s">
         <v>11</v>
@@ -20784,7 +20796,7 @@
         <v>2024.0</v>
       </c>
       <c r="G380" s="16" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H380" s="15"/>
       <c r="I380" s="15"/>
@@ -20855,7 +20867,7 @@
         <v>871</v>
       </c>
       <c r="B382" s="15" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C382" s="15" t="s">
         <v>9</v>
@@ -21247,7 +21259,7 @@
       <c r="C391" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="D391" s="15" t="s">
+      <c r="D391" s="13" t="s">
         <v>893</v>
       </c>
       <c r="E391" s="15" t="s">
@@ -21257,7 +21269,7 @@
         <v>2025.0</v>
       </c>
       <c r="G391" s="12" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H391" s="15"/>
       <c r="I391" s="15"/>
@@ -21328,7 +21340,7 @@
         <v>897</v>
       </c>
       <c r="B393" s="15" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C393" s="15" t="s">
         <v>25</v>
@@ -21376,8 +21388,8 @@
       <c r="C394" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="D394" s="15" t="s">
-        <v>548</v>
+      <c r="D394" s="13" t="s">
+        <v>549</v>
       </c>
       <c r="E394" s="15" t="s">
         <v>11</v>
@@ -21414,7 +21426,7 @@
         <v>900</v>
       </c>
       <c r="B395" s="15" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C395" s="15" t="s">
         <v>9</v>
@@ -21462,11 +21474,11 @@
       <c r="C396" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="D396" s="15" t="s">
-        <v>339</v>
+      <c r="D396" s="13" t="s">
+        <v>340</v>
       </c>
       <c r="E396" s="15" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="F396" s="11">
         <v>2013.0</v>
@@ -21509,7 +21521,7 @@
         <v>906</v>
       </c>
       <c r="E397" s="15" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="F397" s="11">
         <v>2008.0</v>
@@ -21549,7 +21561,7 @@
         <v>9</v>
       </c>
       <c r="D398" s="15" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E398" s="15" t="s">
         <v>62</v>
@@ -21720,7 +21732,7 @@
       <c r="C402" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="D402" s="15" t="s">
+      <c r="D402" s="13" t="s">
         <v>919</v>
       </c>
       <c r="E402" s="15" t="s">
@@ -21730,7 +21742,7 @@
         <v>2016.0</v>
       </c>
       <c r="G402" s="16" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H402" s="15"/>
       <c r="I402" s="15"/>
@@ -21763,7 +21775,7 @@
       <c r="C403" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="D403" s="15" t="s">
+      <c r="D403" s="13" t="s">
         <v>922</v>
       </c>
       <c r="E403" s="15" t="s">
@@ -21849,7 +21861,7 @@
       <c r="C405" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="D405" s="15" t="s">
+      <c r="D405" s="13" t="s">
         <v>928</v>
       </c>
       <c r="E405" s="15" t="s">
@@ -21892,7 +21904,7 @@
       <c r="C406" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="D406" s="15" t="s">
+      <c r="D406" s="13" t="s">
         <v>932</v>
       </c>
       <c r="E406" s="15" t="s">
@@ -21902,7 +21914,7 @@
         <v>2009.0</v>
       </c>
       <c r="G406" s="16" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H406" s="14"/>
       <c r="I406" s="15"/>
@@ -22188,7 +22200,7 @@
         <v>950</v>
       </c>
       <c r="B413" s="15" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C413" s="15" t="s">
         <v>9</v>
@@ -22231,7 +22243,7 @@
         <v>952</v>
       </c>
       <c r="B414" s="15" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C414" s="15" t="s">
         <v>9</v>
@@ -22274,7 +22286,7 @@
         <v>954</v>
       </c>
       <c r="B415" s="15" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C415" s="15" t="s">
         <v>9</v>
@@ -22322,8 +22334,8 @@
       <c r="C416" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="D416" s="15" t="s">
-        <v>568</v>
+      <c r="D416" s="13" t="s">
+        <v>569</v>
       </c>
       <c r="E416" s="15" t="s">
         <v>11</v>
@@ -22408,7 +22420,7 @@
       <c r="C418" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="D418" s="15" t="s">
+      <c r="D418" s="13" t="s">
         <v>960</v>
       </c>
       <c r="E418" s="15" t="s">
@@ -22418,7 +22430,7 @@
         <v>2025.0</v>
       </c>
       <c r="G418" s="16" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H418" s="15"/>
       <c r="I418" s="15"/>
@@ -22489,7 +22501,7 @@
         <v>964</v>
       </c>
       <c r="B420" s="15" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C420" s="15" t="s">
         <v>9</v>
@@ -22676,7 +22688,7 @@
         <v>1970.0</v>
       </c>
       <c r="G424" s="16" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H424" s="15"/>
       <c r="I424" s="15"/>
@@ -22795,7 +22807,7 @@
       <c r="C427" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="D427" s="15" t="s">
+      <c r="D427" s="13" t="s">
         <v>985</v>
       </c>
       <c r="E427" s="15" t="s">
@@ -22881,7 +22893,7 @@
       <c r="C429" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="D429" s="15" t="s">
+      <c r="D429" s="13" t="s">
         <v>991</v>
       </c>
       <c r="E429" s="15" t="s">
@@ -23263,13 +23275,13 @@
         <v>1013</v>
       </c>
       <c r="B438" s="13" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C438" s="13" t="s">
         <v>9</v>
       </c>
       <c r="D438" s="13" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E438" s="13" t="s">
         <v>11</v>
@@ -23364,7 +23376,7 @@
         <v>1999.0</v>
       </c>
       <c r="G440" s="12" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H440" s="15"/>
       <c r="I440" s="13"/>
@@ -23607,7 +23619,7 @@
         <v>1031</v>
       </c>
       <c r="B446" s="13" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C446" s="13" t="s">
         <v>9</v>
@@ -23650,13 +23662,13 @@
         <v>1033</v>
       </c>
       <c r="B447" s="13" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C447" s="13" t="s">
         <v>9</v>
       </c>
       <c r="D447" s="13" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E447" s="13" t="s">
         <v>11</v>
@@ -23696,7 +23708,7 @@
         <v>1035</v>
       </c>
       <c r="C448" s="13" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D448" s="13" t="s">
         <v>1036</v>
@@ -23913,8 +23925,8 @@
       <c r="C453" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="D453" s="14" t="s">
-        <v>568</v>
+      <c r="D453" s="13" t="s">
+        <v>569</v>
       </c>
       <c r="E453" s="13" t="s">
         <v>62</v>
@@ -24166,7 +24178,7 @@
         <v>1062</v>
       </c>
       <c r="B459" s="13" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C459" s="13" t="s">
         <v>9</v>
@@ -24553,7 +24565,7 @@
         <v>1081</v>
       </c>
       <c r="B468" s="15" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C468" s="15" t="s">
         <v>25</v>
@@ -24983,7 +24995,7 @@
         <v>1111</v>
       </c>
       <c r="B478" s="13" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C478" s="13" t="s">
         <v>9</v>
@@ -25026,7 +25038,7 @@
         <v>1113</v>
       </c>
       <c r="B479" s="13" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C479" s="13" t="s">
         <v>9</v>
@@ -25342,7 +25354,7 @@
         <v>2022.0</v>
       </c>
       <c r="G486" s="16" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H486" s="15"/>
       <c r="I486" s="14"/>
@@ -25548,7 +25560,7 @@
         <v>9</v>
       </c>
       <c r="D491" s="13" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="E491" s="13" t="s">
         <v>1104</v>
@@ -25585,7 +25597,7 @@
         <v>1145</v>
       </c>
       <c r="B492" s="13" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C492" s="13" t="s">
         <v>9</v>
@@ -25972,7 +25984,7 @@
         <v>1168</v>
       </c>
       <c r="B501" s="13" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C501" s="13" t="s">
         <v>9</v>
@@ -26316,7 +26328,7 @@
         <v>1188</v>
       </c>
       <c r="B509" s="13" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C509" s="13" t="s">
         <v>9</v>
@@ -26534,7 +26546,7 @@
         <v>1202</v>
       </c>
       <c r="C514" s="15" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D514" s="15" t="s">
         <v>1203</v>
@@ -26632,7 +26644,7 @@
         <v>2019.0</v>
       </c>
       <c r="G516" s="16" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H516" s="15"/>
       <c r="I516" s="14"/>
@@ -26665,7 +26677,7 @@
       <c r="C517" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="D517" s="15" t="s">
+      <c r="D517" s="13" t="s">
         <v>1212</v>
       </c>
       <c r="E517" s="15" t="s">
@@ -27090,7 +27102,7 @@
         <v>1236</v>
       </c>
       <c r="B527" s="13" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C527" s="13" t="s">
         <v>9</v>
@@ -27348,7 +27360,7 @@
         <v>1249</v>
       </c>
       <c r="B533" s="13" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C533" s="13" t="s">
         <v>9</v>
@@ -28935,13 +28947,27 @@
       <c r="AA569" s="8"/>
     </row>
     <row r="570">
-      <c r="A570" s="14"/>
-      <c r="B570" s="14"/>
-      <c r="C570" s="14"/>
-      <c r="D570" s="14"/>
-      <c r="E570" s="14"/>
-      <c r="F570" s="14"/>
-      <c r="G570" s="16"/>
+      <c r="A570" s="13" t="s">
+        <v>1337</v>
+      </c>
+      <c r="B570" s="13" t="s">
+        <v>1338</v>
+      </c>
+      <c r="C570" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="D570" s="13" t="s">
+        <v>1339</v>
+      </c>
+      <c r="E570" s="13" t="s">
+        <v>1340</v>
+      </c>
+      <c r="F570" s="13">
+        <v>2019.0</v>
+      </c>
+      <c r="G570" s="12" t="s">
+        <v>14</v>
+      </c>
       <c r="H570" s="14"/>
       <c r="I570" s="14"/>
       <c r="J570" s="14"/>

--- a/Albums List.xlsx
+++ b/Albums List.xlsx
@@ -2935,7 +2935,7 @@
     <t>Ep.01-Causa</t>
   </si>
   <si>
-    <t>DELLAFUENTE, Taifa Yallah</t>
+    <t>DELLAFUENTE; Taifa Yallah</t>
   </si>
   <si>
     <t>Rock, Argentinean Rock, Hiphop/Rap</t>
@@ -22543,7 +22543,7 @@
       <c r="A421" s="15" t="s">
         <v>965</v>
       </c>
-      <c r="B421" s="15" t="s">
+      <c r="B421" s="13" t="s">
         <v>966</v>
       </c>
       <c r="C421" s="15" t="s">

--- a/Albums List.xlsx
+++ b/Albums List.xlsx
@@ -13830,7 +13830,7 @@
         <v>2011.0</v>
       </c>
       <c r="G218" s="12" t="s">
-        <v>162</v>
+        <v>18</v>
       </c>
       <c r="H218" s="15"/>
       <c r="I218" s="17"/>
@@ -21397,8 +21397,8 @@
       <c r="F394" s="11">
         <v>2025.0</v>
       </c>
-      <c r="G394" s="16" t="s">
-        <v>116</v>
+      <c r="G394" s="12" t="s">
+        <v>22</v>
       </c>
       <c r="H394" s="15"/>
       <c r="I394" s="15"/>
